--- a/SGC-CKN/Excel/0da22204-8bb7-4d93-aa5e-9c51bd3dd66c_Hạng_mục__Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P7-139_D800_08-04-2026.xlsx
+++ b/SGC-CKN/Excel/0da22204-8bb7-4d93-aa5e-9c51bd3dd66c_Hạng_mục__Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P7-139_D800_08-04-2026.xlsx
@@ -98,7 +98,7 @@
     <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">09:50
+    <t xml:space="preserve">09:30
 08/04/2026</t>
   </si>
   <si>
@@ -119,7 +119,7 @@
 08/04/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">12:02
+    <t xml:space="preserve">10:02
 08/04/2026</t>
   </si>
   <si>
@@ -132,7 +132,7 @@
     <t>Sét xám trắng, xám xanh dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">10:01
+    <t xml:space="preserve">10:03
 08/04/2026</t>
   </si>
   <si>
@@ -170,7 +170,7 @@
 08/04/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">13:47
+    <t xml:space="preserve">13:44
 08/04/2026</t>
   </si>
   <si>
@@ -299,7 +299,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -336,12 +336,6 @@
     </font>
     <font>
       <color rgb="FF78350F"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -398,7 +392,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -433,11 +427,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFDE68A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -578,7 +567,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -616,6 +605,12 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -625,17 +620,17 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -682,22 +677,13 @@
     <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1289,13 +1275,13 @@
         <v>-7.09</v>
       </c>
       <c r="H11" s="5">
-        <v>0.07</v>
+        <v>0.4</v>
       </c>
       <c r="I11" s="5">
         <v>7.72</v>
       </c>
       <c r="J11" s="8">
-        <v>115.8</v>
+        <v>19.3</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1324,312 +1310,312 @@
         <v>-9.09</v>
       </c>
       <c r="H12" s="9">
-        <v>2.12</v>
+        <v>0.12</v>
       </c>
       <c r="I12" s="9">
         <v>2</v>
       </c>
-      <c r="J12" s="12">
-        <v>0.94</v>
+      <c r="J12" s="8">
+        <v>17.14</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="12">
         <v>-9.09</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="12">
         <v>-19.19</v>
       </c>
-      <c r="H13" s="13">
-        <v>1.3</v>
-      </c>
-      <c r="I13" s="13">
+      <c r="H13" s="12">
+        <v>1.27</v>
+      </c>
+      <c r="I13" s="12">
         <v>10.1</v>
       </c>
       <c r="J13" s="8">
-        <v>7.77</v>
-      </c>
-      <c r="K13" s="14" t="s">
+        <v>7.97</v>
+      </c>
+      <c r="K13" s="13" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="15">
         <v>-19.19</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="15">
         <v>-21.59</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="15">
         <v>0.72</v>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="15">
         <v>2.4</v>
       </c>
-      <c r="J14" s="19">
+      <c r="J14" s="18">
         <v>3.35</v>
       </c>
-      <c r="K14" s="17" t="s">
+      <c r="K14" s="16" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C15" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="D15" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="E15" s="22" t="s">
+      <c r="E15" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="19">
         <v>-21.59</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="19">
         <v>-26.59</v>
       </c>
-      <c r="H15" s="20">
-        <v>0.78</v>
-      </c>
-      <c r="I15" s="20">
+      <c r="H15" s="19">
+        <v>0.73</v>
+      </c>
+      <c r="I15" s="19">
         <v>5</v>
       </c>
       <c r="J15" s="8">
-        <v>6.38</v>
-      </c>
-      <c r="K15" s="21" t="s">
+        <v>6.82</v>
+      </c>
+      <c r="K15" s="20" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="25" t="s">
+      <c r="D16" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="E16" s="25" t="s">
+      <c r="E16" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="23">
+      <c r="F16" s="22">
         <v>-26.59</v>
       </c>
-      <c r="G16" s="23">
+      <c r="G16" s="22">
         <v>-36.52</v>
       </c>
-      <c r="H16" s="23">
+      <c r="H16" s="22">
         <v>1.45</v>
       </c>
-      <c r="I16" s="23">
+      <c r="I16" s="22">
         <v>9.93</v>
       </c>
       <c r="J16" s="8">
         <v>6.85</v>
       </c>
-      <c r="K16" s="24" t="s">
+      <c r="K16" s="23" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="E17" s="28" t="s">
+      <c r="E17" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="25">
         <v>-36.52</v>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="25">
         <v>-38.52</v>
       </c>
-      <c r="H17" s="26">
+      <c r="H17" s="25">
         <v>0.32</v>
       </c>
-      <c r="I17" s="26">
+      <c r="I17" s="25">
         <v>2</v>
       </c>
       <c r="J17" s="8">
         <v>6.32</v>
       </c>
-      <c r="K17" s="27" t="s">
+      <c r="K17" s="26" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="C18" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="E18" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="28">
         <v>-38.52</v>
       </c>
-      <c r="G18" s="29">
+      <c r="G18" s="28">
         <v>-39.71</v>
       </c>
-      <c r="H18" s="29">
+      <c r="H18" s="28">
         <v>0.2</v>
       </c>
-      <c r="I18" s="29">
+      <c r="I18" s="28">
         <v>1.19</v>
       </c>
       <c r="J18" s="8">
         <v>5.95</v>
       </c>
-      <c r="K18" s="30" t="s">
+      <c r="K18" s="29" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="32" t="s">
+      <c r="A19" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="B19" s="32" t="s">
+      <c r="B19" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="33" t="s">
+      <c r="C19" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="D19" s="34" t="s">
+      <c r="D19" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="E19" s="34" t="s">
+      <c r="E19" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="F19" s="32">
+      <c r="F19" s="31">
         <v>-39.71</v>
       </c>
-      <c r="G19" s="32">
+      <c r="G19" s="31">
         <v>-48.7</v>
       </c>
-      <c r="H19" s="32">
+      <c r="H19" s="31">
         <v>1.07</v>
       </c>
-      <c r="I19" s="32">
+      <c r="I19" s="31">
         <v>8.99</v>
       </c>
       <c r="J19" s="8">
         <v>8.43</v>
       </c>
-      <c r="K19" s="33" t="s">
+      <c r="K19" s="32" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="35" t="s">
+      <c r="A20" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="35" t="s">
+      <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="36" t="s">
+      <c r="C20" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="37" t="s">
+      <c r="D20" s="36" t="s">
         <v>73</v>
       </c>
-      <c r="E20" s="37" t="s">
+      <c r="E20" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="F20" s="35">
+      <c r="F20" s="34">
         <v>-48.7</v>
       </c>
-      <c r="G20" s="35">
+      <c r="G20" s="34">
         <v>-49.85</v>
       </c>
-      <c r="H20" s="35">
+      <c r="H20" s="34">
         <v>0.27</v>
       </c>
-      <c r="I20" s="35">
+      <c r="I20" s="34">
         <v>1.15</v>
       </c>
-      <c r="J20" s="19">
+      <c r="J20" s="18">
         <v>4.31</v>
       </c>
-      <c r="K20" s="36" t="s">
+      <c r="K20" s="35" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="38" t="s">
+      <c r="A23" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="37"/>
     </row>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1771,13 +1757,13 @@
         <v>-7.09</v>
       </c>
       <c r="G2" s="5">
-        <v>0.07</v>
+        <v>0.4</v>
       </c>
       <c r="H2" s="5">
         <v>7.72</v>
       </c>
       <c r="I2" s="8">
-        <v>115.8</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1800,125 +1786,125 @@
         <v>-9.09</v>
       </c>
       <c r="G3" s="9">
-        <v>2.12</v>
+        <v>0.12</v>
       </c>
       <c r="H3" s="9">
         <v>2</v>
       </c>
-      <c r="I3" s="12">
-        <v>0.94</v>
+      <c r="I3" s="8">
+        <v>17.14</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>1</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="12">
         <v>-9.09</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="12">
         <v>-19.19</v>
       </c>
-      <c r="G4" s="13">
-        <v>1.3</v>
-      </c>
-      <c r="H4" s="13">
+      <c r="G4" s="12">
+        <v>1.27</v>
+      </c>
+      <c r="H4" s="12">
         <v>10.1</v>
       </c>
       <c r="I4" s="8">
-        <v>7.77</v>
+        <v>7.97</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
+      <c r="A5" s="15">
         <v>4</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="15">
         <v>1</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="15">
         <v>-19.19</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="15">
         <v>-21.59</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="15">
         <v>0.72</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="15">
         <v>2.4</v>
       </c>
-      <c r="I5" s="19">
+      <c r="I5" s="18">
         <v>3.35</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="20">
+      <c r="A6" s="19">
         <v>5</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="19">
         <v>1</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="19">
         <v>-21.59</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="19">
         <v>-26.59</v>
       </c>
-      <c r="G6" s="20">
-        <v>0.78</v>
-      </c>
-      <c r="H6" s="20">
+      <c r="G6" s="19">
+        <v>0.73</v>
+      </c>
+      <c r="H6" s="19">
         <v>5</v>
       </c>
       <c r="I6" s="8">
-        <v>6.38</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="23">
+      <c r="A7" s="22">
         <v>6</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="22">
         <v>1</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="22">
         <v>-26.59</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="22">
         <v>-36.52</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="22">
         <v>1.45</v>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="22">
         <v>9.93</v>
       </c>
       <c r="I7" s="8">
@@ -1926,28 +1912,28 @@
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="26">
+      <c r="A8" s="25">
         <v>7</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="25">
         <v>1</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="25">
         <v>-36.52</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="25">
         <v>-38.52</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="25">
         <v>0.32</v>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="25">
         <v>2</v>
       </c>
       <c r="I8" s="8">
@@ -1955,28 +1941,28 @@
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="29">
+      <c r="A9" s="28">
         <v>8</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="28">
         <v>1</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="28">
         <v>-38.52</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="28">
         <v>-39.71</v>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="28">
         <v>0.2</v>
       </c>
-      <c r="H9" s="29">
+      <c r="H9" s="28">
         <v>1.19</v>
       </c>
       <c r="I9" s="8">
@@ -1984,28 +1970,28 @@
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="32">
+      <c r="A10" s="31">
         <v>9</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="31">
         <v>1</v>
       </c>
-      <c r="E10" s="32">
+      <c r="E10" s="31">
         <v>-39.71</v>
       </c>
-      <c r="F10" s="32">
+      <c r="F10" s="31">
         <v>-48.7</v>
       </c>
-      <c r="G10" s="32">
+      <c r="G10" s="31">
         <v>1.07</v>
       </c>
-      <c r="H10" s="32">
+      <c r="H10" s="31">
         <v>8.99</v>
       </c>
       <c r="I10" s="8">
@@ -2013,61 +1999,61 @@
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="35">
+      <c r="A11" s="34">
         <v>10</v>
       </c>
-      <c r="B11" s="35" t="s">
+      <c r="B11" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="34">
         <v>1</v>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="34">
         <v>-48.7</v>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="34">
         <v>-49.85</v>
       </c>
-      <c r="G11" s="35">
+      <c r="G11" s="34">
         <v>0.27</v>
       </c>
-      <c r="H11" s="35">
+      <c r="H11" s="34">
         <v>1.15</v>
       </c>
-      <c r="I11" s="19">
+      <c r="I11" s="18">
         <v>4.31</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="39" t="s">
+      <c r="A12" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="B12" s="40" t="s">
+      <c r="B12" s="39" t="s">
         <v>86</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="39" t="s">
         <v>86</v>
       </c>
-      <c r="D12" s="40">
+      <c r="D12" s="39">
         <v>10</v>
       </c>
-      <c r="E12" s="40">
+      <c r="E12" s="39">
         <v>0.63</v>
       </c>
-      <c r="F12" s="40">
+      <c r="F12" s="39">
         <v>-49.85</v>
       </c>
-      <c r="G12" s="40">
-        <v>8.28</v>
-      </c>
-      <c r="H12" s="40">
+      <c r="G12" s="39">
+        <v>6.53</v>
+      </c>
+      <c r="H12" s="39">
         <v>50.48</v>
       </c>
-      <c r="I12" s="40">
-        <v>6.09</v>
+      <c r="I12" s="39">
+        <v>7.73</v>
       </c>
     </row>
   </sheetData>
